--- a/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
+++ b/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
@@ -1649,7 +1649,7 @@
       <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1660,7 +1660,7 @@
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1671,7 +1671,7 @@
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -1682,7 +1682,7 @@
       <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -1693,7 +1693,7 @@
       <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -1704,7 +1704,7 @@
       <c r="A9" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1715,7 +1715,7 @@
       <c r="A10" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1726,7 +1726,7 @@
       <c r="A11" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="3" t="s">

--- a/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
+++ b/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
@@ -1737,7 +1737,7 @@
       <c r="A12" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1748,7 +1748,7 @@
       <c r="A13" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1759,7 +1759,7 @@
       <c r="A14" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1770,7 +1770,7 @@
       <c r="A15" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1781,7 +1781,7 @@
       <c r="A16" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1792,7 +1792,7 @@
       <c r="A17" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1803,7 +1803,7 @@
       <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1814,7 +1814,7 @@
       <c r="A19" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1825,7 +1825,7 @@
       <c r="A20" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1836,7 +1836,7 @@
       <c r="A21" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1847,7 +1847,7 @@
       <c r="A22" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1858,7 +1858,7 @@
       <c r="A23" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1869,7 +1869,7 @@
       <c r="A24" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="3" t="s">

--- a/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
+++ b/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
@@ -1880,7 +1880,7 @@
       <c r="A25" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -1891,7 +1891,7 @@
       <c r="A26" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -1902,7 +1902,7 @@
       <c r="A27" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -1913,7 +1913,7 @@
       <c r="A28" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -1924,7 +1924,7 @@
       <c r="A29" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -1935,7 +1935,7 @@
       <c r="A30" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -1946,7 +1946,7 @@
       <c r="A31" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -1957,7 +1957,7 @@
       <c r="A32" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -1968,7 +1968,7 @@
       <c r="A33" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C33" s="3" t="s">
@@ -1979,7 +1979,7 @@
       <c r="A34" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -1990,7 +1990,7 @@
       <c r="A35" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C35" s="3" t="s">

--- a/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
+++ b/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
@@ -2001,7 +2001,7 @@
       <c r="A36" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C36" s="3" t="s">
@@ -2012,7 +2012,7 @@
       <c r="A37" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C37" s="3" t="s">

--- a/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
+++ b/C_20001_NeonPoolCharm/JS_to_TS_BatchList.xlsx
@@ -1248,7 +1248,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1257,7 +1257,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2023,7 +2022,7 @@
       <c r="A38" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C38" s="3" t="s">
